--- a/templates/mau-1.xlsx
+++ b/templates/mau-1.xlsx
@@ -491,7 +491,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9372600" cy="1257300"/>
+    <xdr:ext cx="9978875" cy="1257300"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image1.png"/>
